--- a/public/assets/BOs/Susanoo.xlsx
+++ b/public/assets/BOs/Susanoo.xlsx
@@ -5,15 +5,16 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Chris\OneDrive\Github\DoD\DeitiesOfDeath\public\assets\BOs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\doc\coding\DoD\DeitiesOfDeath\public\assets\BOs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92410367-96C5-4F7C-B568-309251B62D96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD8C76A5-9137-4F27-BE7A-E014916A9373}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="43200" windowHeight="23445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
+    <sheet name="Feuil1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="52">
   <si>
     <t>Archaic</t>
   </si>
@@ -111,17 +112,100 @@
 in Classical, fight early and often, and use God Powers to increase Bushido and get those favor chunks. Once you pass Bushido tier 3 you may get favor starved so start spending favor efficiently in late Heroic. </t>
   </si>
   <si>
-    <t>Susanoo Minakatatomi One Base - By BqvH</t>
-  </si>
-  <si>
     <t>Advance - Minakatatomi (3.25)</t>
+  </si>
+  <si>
+    <t>First 3 commoners go to hunt</t>
+  </si>
+  <si>
+    <t>4/0/0/1</t>
+  </si>
+  <si>
+    <t>1 commoner goes to hunt as well</t>
+  </si>
+  <si>
+    <t>4/0/2/1</t>
+  </si>
+  <si>
+    <t>2 commoners to gold</t>
+  </si>
+  <si>
+    <t>The second commoner to gold builds a house nearby</t>
+  </si>
+  <si>
+    <t>4/2/2/1</t>
+  </si>
+  <si>
+    <t>2 commoners to wood</t>
+  </si>
+  <si>
+    <t>7/2/2/1</t>
+  </si>
+  <si>
+    <t>3 commoners to food</t>
+  </si>
+  <si>
+    <t>Build the temple either with the miko or with a gold villager</t>
+  </si>
+  <si>
+    <t>7/3/2/1</t>
+  </si>
+  <si>
+    <t>1 commoner to wood</t>
+  </si>
+  <si>
+    <t>7/3/4/1</t>
+  </si>
+  <si>
+    <t>Advance with Inari Okami (3.18)</t>
+  </si>
+  <si>
+    <t>Build a house with a food villager. 
+Research Sacred Custodians from a Shrine and gather nearby relics with the starting miko</t>
+  </si>
+  <si>
+    <t>Classical (4.03 because Tsukuyomi ages up 25% faster)</t>
+  </si>
+  <si>
+    <t>7/3/4/2</t>
+  </si>
+  <si>
+    <t>1 miko to shrine</t>
+  </si>
+  <si>
+    <t>Upon advancing, build a stable + a dojo with a food villager
+Send the 2nd miko either to a build new shrine or to the first shrine if the earlier miko is still gathering relics</t>
+  </si>
+  <si>
+    <t>7/3/5/2</t>
+  </si>
+  <si>
+    <t>1 commoner to gold</t>
+  </si>
+  <si>
+    <t>Train 3 naginata riders (and go raid with them + a kitsune) and then a couple samurai/onna musha</t>
+  </si>
+  <si>
+    <t>x/3/5/2</t>
+  </si>
+  <si>
+    <t>next several commoners to food, then adjust as the game progresses</t>
+  </si>
+  <si>
+    <t>Keep building houses with gold or food villagers as needed</t>
+  </si>
+  <si>
+    <t>Standard 1 TC BO by mMoksha333</t>
+  </si>
+  <si>
+    <t>Minakatatomi One Base - By BqvH</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -167,6 +251,34 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="4">
@@ -202,7 +314,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -217,6 +329,18 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -499,22 +623,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="73.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="179.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="255.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="73.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="179.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="255.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="19.5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="19.8" x14ac:dyDescent="0.4">
       <c r="A1" s="4" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
       <c r="D1" s="5"/>
     </row>
-    <row r="2" spans="1:4" ht="21" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" ht="21" x14ac:dyDescent="0.4">
       <c r="A2" s="6" t="s">
         <v>0</v>
       </c>
@@ -522,7 +646,7 @@
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
     </row>
-    <row r="3" spans="1:4" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -530,7 +654,7 @@
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
@@ -540,7 +664,7 @@
       </c>
       <c r="D4" s="1"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
@@ -552,7 +676,7 @@
       </c>
       <c r="D5" s="1"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>7</v>
       </c>
@@ -562,7 +686,7 @@
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>9</v>
       </c>
@@ -572,7 +696,7 @@
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="3" t="s">
         <v>11</v>
@@ -580,7 +704,7 @@
       <c r="C8" s="3"/>
       <c r="D8" s="1"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>12</v>
       </c>
@@ -590,7 +714,7 @@
       </c>
       <c r="D9" s="1"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>14</v>
       </c>
@@ -600,15 +724,15 @@
       <c r="C10" s="3"/>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" spans="1:4" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A11" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>16</v>
       </c>
@@ -620,7 +744,7 @@
       </c>
       <c r="D12" s="1"/>
     </row>
-    <row r="14" spans="1:4" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A14" s="7" t="s">
         <v>19</v>
       </c>
@@ -628,7 +752,7 @@
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="3" t="s">
@@ -636,7 +760,7 @@
       </c>
       <c r="D15" s="1"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="3" t="s">
@@ -644,7 +768,7 @@
       </c>
       <c r="D16" s="1"/>
     </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B17" s="3" t="s">
         <v>22</v>
       </c>
@@ -659,4 +783,187 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7F13D64-5B80-4357-B7F8-13071F89AC84}">
+  <dimension ref="A1:D17"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" ht="19.2" x14ac:dyDescent="0.35">
+      <c r="A1" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+    </row>
+    <row r="2" spans="1:4" ht="21" x14ac:dyDescent="0.4">
+      <c r="A2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+    </row>
+    <row r="3" spans="1:4" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="11"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="11"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="11"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="11"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="13"/>
+      <c r="D8" s="11"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="11"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="13"/>
+      <c r="D10" s="11"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="13"/>
+      <c r="D11" s="11"/>
+    </row>
+    <row r="12" spans="1:4" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="13"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" s="11"/>
+    </row>
+    <row r="14" spans="1:4" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A14" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="D15" s="11"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" s="11"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>49</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A14:D14"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>